--- a/data/trans_camb/BARTHEL_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/BARTHEL_R2-Habitat-trans_camb.xlsx
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>-1,78</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-3,96</t>
+          <t>3,96</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,01</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-14,15</t>
+          <t>14,15</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-12,51</t>
+          <t>12,51</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-14,72</t>
+          <t>14,72</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>-6,89</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-8,74</t>
+          <t>8,74</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-9,42</t>
+          <t>9,42</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 9,75</t>
+          <t>-9,02; 5,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 5,01</t>
+          <t>-4,24; 11,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 4,69</t>
+          <t>-4,23; 9,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,7; -4,34</t>
+          <t>5,91; 21,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,35; -4,33</t>
+          <t>4,03; 21,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,28; -7,16</t>
+          <t>8,1; 21,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,24; -0,98</t>
+          <t>1,57; 12,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,48; -2,22</t>
+          <t>2,35; 14,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,11; -4,27</t>
+          <t>5,02; 14,27</t>
         </is>
       </c>
     </row>
@@ -730,47 +730,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>-16,8%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-4,43%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-3,37%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-15,85%</t>
+          <t>131,51%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-14,01%</t>
+          <t>116,25%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-16,5%</t>
+          <t>136,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>-7,71%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-9,78%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-10,55%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 11,61</t>
+          <t>-63,69; 79,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 5,88</t>
+          <t>-29,44; 179,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 5,55</t>
+          <t>-29,83; 159,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,4; -5,16</t>
+          <t>35,04; 291,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,63; -4,98</t>
+          <t>19,21; 275,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,34; -8,77</t>
+          <t>45,72; 319,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,44; -1,15</t>
+          <t>9,27; 152,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,93; -2,61</t>
+          <t>15,12; 173,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-15,28; -4,97</t>
+          <t>35,1; 184,87</t>
         </is>
       </c>
     </row>
@@ -840,47 +840,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-12,89</t>
+          <t>12,89</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-4,73</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-7,62</t>
+          <t>7,62</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-17,59</t>
+          <t>17,59</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-3,59</t>
+          <t>3,59</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,94</t>
+          <t>8,94</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>-15,47</t>
+          <t>15,47</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-4,18</t>
+          <t>4,18</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-8,51</t>
+          <t>8,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,19; -4,73</t>
+          <t>5,03; 21,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 1,77</t>
+          <t>-1,94; 11,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,45; -1,08</t>
+          <t>1,21; 14,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,73; -8,17</t>
+          <t>8,45; 26,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 4,72</t>
+          <t>-3,53; 12,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,25; -1,45</t>
+          <t>2,24; 15,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-22,07; -9,42</t>
+          <t>9,76; 21,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 1,64</t>
+          <t>-1,53; 9,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,09; -3,22</t>
+          <t>3,76; 12,9</t>
         </is>
       </c>
     </row>
@@ -946,47 +946,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-14,02%</t>
+          <t>160,31%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-5,14%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-8,28%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-20,67%</t>
+          <t>117,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-4,22%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-10,5%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-17,55%</t>
+          <t>130,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-4,74%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-9,65%</t>
+          <t>71,74%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,83; -5,78</t>
+          <t>35,32; 443,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 1,94</t>
+          <t>-19,11; 267,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,32; -1,23</t>
+          <t>4,45; 290,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,91; -10,19</t>
+          <t>40,99; 246,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 5,63</t>
+          <t>-21,11; 122,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,27; -1,61</t>
+          <t>9,2; 140,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,52; -11,03</t>
+          <t>63,35; 235,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 1,97</t>
+          <t>-11,47; 107,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,43; -3,86</t>
+          <t>24,29; 142,59</t>
         </is>
       </c>
     </row>
@@ -1056,47 +1056,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-11,08</t>
+          <t>11,08</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-7,25</t>
+          <t>7,25</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-7,88</t>
+          <t>7,88</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-16,75</t>
+          <t>16,75</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-13,92</t>
+          <t>13,92</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>-2,74</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>-14,44</t>
+          <t>14,44</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-10,84</t>
+          <t>10,84</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>1,48</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,32; -2,79</t>
+          <t>2,69; 20,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,07; -0,68</t>
+          <t>0,99; 13,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,69; -1,92</t>
+          <t>2,0; 13,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,87; -7,27</t>
+          <t>6,86; 26,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,96; -4,07</t>
+          <t>4,92; 24,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 14,66</t>
+          <t>-15,96; 10,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-21,67; -7,7</t>
+          <t>7,31; 21,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,96; -4,84</t>
+          <t>4,61; 17,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 7,89</t>
+          <t>-7,82; 9,85</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-11,49%</t>
+          <t>311,69%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-7,52%</t>
+          <t>203,99%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-8,17%</t>
+          <t>221,57%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-18,97%</t>
+          <t>143,15%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-15,76%</t>
+          <t>118,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>-23,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>-15,72%</t>
+          <t>176,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-11,81%</t>
+          <t>132,86%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-1,61%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,02; -2,92</t>
+          <t>16,42; 1667,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,45; -0,87</t>
+          <t>0,4; 1186,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,16; -2,15</t>
+          <t>14,64; 1264,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,38; -8,81</t>
+          <t>37,01; 331,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,5; -5,15</t>
+          <t>26,14; 311,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 18,05</t>
+          <t>-86,35; 110,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,37; -8,61</t>
+          <t>62,46; 368,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,08; -5,32</t>
+          <t>39,42; 301,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 9,02</t>
+          <t>-63,18; 146,89</t>
         </is>
       </c>
     </row>
@@ -1272,47 +1272,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-5,69</t>
+          <t>5,69</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,99</t>
+          <t>2,99</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-4,66</t>
+          <t>4,66</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-5,88</t>
+          <t>5,88</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,24</t>
+          <t>6,24</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>-5,06</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-3,54</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,65</t>
+          <t>4,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 1,37</t>
+          <t>-1,67; 13,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 5,88</t>
+          <t>-5,86; 6,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 2,75</t>
+          <t>-3,54; 8,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 2,45</t>
+          <t>-3,24; 12,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 1,8</t>
+          <t>-1,6; 14,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 0,17</t>
+          <t>0,05; 12,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 0,12</t>
+          <t>-0,28; 10,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 1,63</t>
+          <t>-1,95; 8,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -0,58</t>
+          <t>-0,46; 8,77</t>
         </is>
       </c>
     </row>
@@ -1378,47 +1378,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-6,25%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-0,68%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-3,29%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-5,5%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-6,94%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-7,36%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>-5,8%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-4,06%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-5,33%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 1,53</t>
+          <t>-17,19; 220,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 6,63</t>
+          <t>-50,27; 119,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 3,11</t>
+          <t>-27,63; 152,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 2,99</t>
+          <t>-16,46; 101,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 2,05</t>
+          <t>-10,15; 117,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 0,19</t>
+          <t>-1,66; 113,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 0,11</t>
+          <t>-1,91; 105,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 1,85</t>
+          <t>-14,41; 82,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,25; -0,69</t>
+          <t>-3,95; 88,46</t>
         </is>
       </c>
     </row>
@@ -1488,47 +1488,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-6,99</t>
+          <t>6,99</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-3,91</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-5,19</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-12,44</t>
+          <t>12,44</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-8,23</t>
+          <t>8,23</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,84</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>-10,08</t>
+          <t>10,08</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-6,34</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,19</t>
+          <t>5,19</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,81; -2,97</t>
+          <t>2,99; 10,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,29; -0,33</t>
+          <t>0,31; 7,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,36; -2,02</t>
+          <t>2,11; 8,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,79; -7,81</t>
+          <t>8,25; 16,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,24; -3,82</t>
+          <t>4,06; 12,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 4,74</t>
+          <t>-4,5; 10,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,97; -7,18</t>
+          <t>7,18; 12,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -3,35</t>
+          <t>3,66; 9,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 0,46</t>
+          <t>-1,59; 8,36</t>
         </is>
       </c>
     </row>
@@ -1594,47 +1594,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-7,59%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-4,25%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-5,63%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-14,38%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-9,51%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-5,59%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>-11,34%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>-7,13%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-5,84%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -3,35</t>
+          <t>30,18; 167,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-7,78; -0,36</t>
+          <t>2,59; 107,08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,89; -2,22</t>
+          <t>18,31; 127,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -9,59</t>
+          <t>53,01; 148,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-13,84; -4,53</t>
+          <t>24,72; 107,54</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 5,53</t>
+          <t>-28,38; 85,25</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,43; -8,1</t>
+          <t>57,68; 133,08</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -3,86</t>
+          <t>30,0; 94,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 0,81</t>
+          <t>-7,17; 83,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/BARTHEL_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/BARTHEL_R2-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,01</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,72</t>
+          <t>14,67</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,42</t>
+          <t>8,84</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 5,49</t>
+          <t>-9,6; 4,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 11,86</t>
+          <t>-3,64; 12,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 9,91</t>
+          <t>-5,26; 7,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,91; 21,93</t>
+          <t>6,6; 23,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 21,61</t>
+          <t>3,8; 21,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 21,04</t>
+          <t>7,58; 20,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 12,54</t>
+          <t>0,77; 12,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,38</t>
+          <t>2,99; 14,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 14,27</t>
+          <t>3,91; 13,64</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>136,83%</t>
+          <t>136,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>82,66%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-63,69; 79,01</t>
+          <t>-64,55; 78,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,44; 179,38</t>
+          <t>-29,08; 181,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,83; 159,53</t>
+          <t>-35,27; 119,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,04; 291,58</t>
+          <t>40,63; 321,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,21; 275,18</t>
+          <t>22,1; 308,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,72; 319,95</t>
+          <t>47,12; 313,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 152,43</t>
+          <t>4,01; 161,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,12; 173,35</t>
+          <t>22,44; 175,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,1; 184,87</t>
+          <t>27,53; 171,93</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>7,22</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,94</t>
+          <t>8,66</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,51</t>
+          <t>8,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 21,31</t>
+          <t>5,09; 21,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 11,43</t>
+          <t>-1,2; 11,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 14,02</t>
+          <t>0,57; 13,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,45; 26,34</t>
+          <t>8,68; 26,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 12,6</t>
+          <t>-4,67; 11,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 15,17</t>
+          <t>1,36; 15,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 21,67</t>
+          <t>9,6; 21,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 9,75</t>
+          <t>-1,22; 9,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 12,9</t>
+          <t>3,26; 12,6</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,32; 443,33</t>
+          <t>38,9; 400,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 267,91</t>
+          <t>-15,75; 235,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 290,98</t>
+          <t>0,49; 281,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40,99; 246,91</t>
+          <t>42,97; 241,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 122,19</t>
+          <t>-24,5; 99,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,2; 140,53</t>
+          <t>7,07; 141,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,35; 235,41</t>
+          <t>60,31; 230,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 107,79</t>
+          <t>-8,8; 103,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,29; 142,59</t>
+          <t>21,22; 142,14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,88</t>
+          <t>7,36</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,74</t>
+          <t>9,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>7,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 20,68</t>
+          <t>3,65; 21,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 13,99</t>
+          <t>0,52; 14,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 13,54</t>
+          <t>1,59; 12,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 26,09</t>
+          <t>6,67; 26,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 24,43</t>
+          <t>4,34; 23,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 10,91</t>
+          <t>1,59; 16,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,31; 21,07</t>
+          <t>7,65; 20,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 17,23</t>
+          <t>4,51; 17,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 9,85</t>
+          <t>2,92; 13,1</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>221,57%</t>
+          <t>206,83%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-23,45%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,42; 1667,8</t>
+          <t>35,24; 1612,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1186,85</t>
+          <t>-9,45; 1129,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,64; 1264,54</t>
+          <t>4,33; 1198,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37,01; 331,07</t>
+          <t>37,18; 347,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,14; 311,12</t>
+          <t>24,61; 301,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,35; 110,94</t>
+          <t>5,6; 218,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,46; 368,37</t>
+          <t>68,17; 370,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39,42; 301,88</t>
+          <t>39,01; 308,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,18; 146,89</t>
+          <t>24,39; 254,54</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,99</t>
+          <t>2,86</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,24</t>
+          <t>7,06</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,65</t>
+          <t>5,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 13,52</t>
+          <t>-1,2; 13,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 6,95</t>
+          <t>-5,93; 6,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 8,27</t>
+          <t>-4,06; 8,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 12,0</t>
+          <t>-3,03; 11,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 14,04</t>
+          <t>-2,49; 13,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 12,38</t>
+          <t>0,55; 13,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 10,46</t>
+          <t>0,07; 10,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 8,62</t>
+          <t>-1,69; 9,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 8,77</t>
+          <t>0,48; 9,29</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 220,65</t>
+          <t>-14,05; 219,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,27; 119,48</t>
+          <t>-49,52; 97,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 152,7</t>
+          <t>-32,97; 143,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 101,27</t>
+          <t>-17,45; 96,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 117,6</t>
+          <t>-14,2; 111,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 113,6</t>
+          <t>2,13; 120,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 105,09</t>
+          <t>-0,18; 101,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 82,83</t>
+          <t>-13,13; 87,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 88,46</t>
+          <t>2,0; 93,45</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>4,71</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>9,57</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>7,32</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,99; 10,37</t>
+          <t>3,09; 10,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 7,05</t>
+          <t>0,53; 7,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,11; 8,34</t>
+          <t>1,52; 7,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,25; 16,95</t>
+          <t>8,12; 16,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,06; 12,52</t>
+          <t>3,89; 12,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 10,56</t>
+          <t>6,37; 13,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,18; 12,99</t>
+          <t>7,09; 13,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,1</t>
+          <t>3,59; 9,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 8,36</t>
+          <t>4,71; 9,86</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>30,18; 167,72</t>
+          <t>30,64; 168,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2,59; 107,08</t>
+          <t>5,34; 115,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18,31; 127,91</t>
+          <t>14,8; 125,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53,01; 148,31</t>
+          <t>50,61; 147,56</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>24,72; 107,54</t>
+          <t>24,13; 110,88</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 85,25</t>
+          <t>41,06; 118,02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,68; 133,08</t>
+          <t>56,37; 133,21</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>30,0; 94,43</t>
+          <t>29,49; 93,4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 83,15</t>
+          <t>35,19; 101,31</t>
         </is>
       </c>
     </row>
